--- a/results/tab02-2.xlsx
+++ b/results/tab02-2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,25 +434,35 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>H22(OLS)+geo+country+region</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>H22(RLM)+full</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>H22(RLM)+geo</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>H22(RLM)+geo+country</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>H22(RLM)+geo+country+region</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>H22(MLM)+geo+country</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>H22(MLM)+geo+country+region</t>
         </is>
@@ -484,29 +494,41 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>4.481***
+[4.414, 4.548]</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>4.011***
 [3.986, 4.037]</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>4.337***
 [4.279, 4.394]</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>4.360***
 [4.298, 4.421]</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4.457***
+[4.391, 4.523]</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>4.319***
 [4.247, 4.391]</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>4.317***
 [4.249, 4.385]</t>
@@ -539,29 +561,41 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>1.962***
+[1.936, 1.989]</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>2.174***
 [2.159, 2.190]</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>1.996***
 [1.970, 2.022]</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>1.996***
 [1.970, 2.022]</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1.974***
+[1.948, 2.000]</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>1.952***
 [1.925, 1.978]</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>1.915***
 [1.887, 1.942]</t>
@@ -594,29 +628,41 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>-0.142***
+[-0.165, -0.120]</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>-0.086***
 [-0.097, -0.075]</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>-0.143***
 [-0.165, -0.121]</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>-0.142***
 [-0.164, -0.121]</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>-0.133***
 [-0.155, -0.111]</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-0.133***
+[-0.155, -0.111]</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>-0.120***
 [-0.142, -0.098]</t>
@@ -637,46 +683,60 @@
 [-0.001, -0.000]</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>-0.000*
+[-0.001, -0.000]</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
         <is>
           <t>-0.001*
 [-0.001, -0.000]</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-0.000⁺
+[-0.001, 0.000]</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Country Var.</t>
+          <t>Region</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>-0.000***
+[-0.000, -0.000]</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.017
-(0.009)</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.006
-(0.008)</t>
-        </is>
-      </c>
+          <t>-0.000***
+[-0.001, -0.000]</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Region Var.</t>
+          <t>Country Var.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -686,9 +746,16 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.019
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.017
+(0.009)</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.006
 (0.008)</t>
         </is>
       </c>
@@ -696,46 +763,78 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Region Var.</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.019
+(0.008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>R² = .68, R²adj = .68, F(2, 35479) = 38497.98, p &lt; .0001, AIC = 66354.5, BIC = 66379.9, LL = -33174.2, MAE = 0.493, MAD = 0.471, N = 35481</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>R² = .74, R²adj = .74, F(2, 7915) = 11128.31, p &lt; .0001, AIC = 15036.1, BIC = 15057.1, LL = -7515.1, MAE = 0.490, MAD = 0.411, N = 7917</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>R² = .74, R²adj = .74, F(3, 7914) = 7424.14, p &lt; .0001, AIC = 15033.3, BIC = 15061.2, LL = -7512.6, MAE = 0.490, MAD = 0.411, N = 7917</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>R² = .74, R²adj = .74, F(4, 7913) = 5613.12, p &lt; .0001, AIC = 14987.4, BIC = 15022.3, LL = -7488.7, MAE = 0.484, MAD = 0.416, N = 7917</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>R² = .70, R²adj = .70, F(2, 35479) = 40952.81, p &lt; .0001, MAE = 0.492, MAD = 0.474, N = 35481</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>R² = .76, R²adj = .76, F(2, 7915) = 12231.37, p &lt; .0001, MAE = 0.490, MAD = 0.418, N = 7917</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>R² = .76, R²adj = .76, F(3, 7914) = 8168.45, p &lt; .0001, MAE = 0.489, MAD = 0.417, N = 7917</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>R² = .76, R²adj = .76, F(4, 7913) = 6173.34, p &lt; .0001, MAE = 0.483, MAD = 0.423, N = 7917</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>R² = .74, R²adj = .74, F(2, 7915) = 11360.92, p &lt; .0001, AIC = 14850.1, BIC = 14884.9, LL = -7420.0, MAE = 0.473, MAD = 0.379, N = 7917, G = 97,
  ICC = 0.04, LRTstat. = 51508.4 (p &lt; .0001)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>R² = .74, R²adj = .74, F(2, 7915) = 11363.27, p &lt; .0001, AIC = 14717.5, BIC = 14759.4, LL = -7352.8, MAE = 0.456, MAD = 0.361, N = 7917, G = 97,
  ICC = 0.02, LRTstat. = 51508.4 (p &lt; .0001)</t>

--- a/results/tab02-2.xlsx
+++ b/results/tab02-2.xlsx
@@ -476,8 +476,8 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4.041***
-[4.015, 4.067]</t>
+          <t>3.942***
+[3.913, 3.971]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -500,8 +500,8 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4.011***
-[3.986, 4.037]</t>
+          <t>3.916***
+[3.888, 3.945]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -543,8 +543,8 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.158***
-[2.142, 2.173]</t>
+          <t>2.255***
+[2.235, 2.274]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -567,8 +567,8 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2.174***
-[2.159, 2.190]</t>
+          <t>2.266***
+[2.247, 2.285]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -610,8 +610,8 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-0.092***
-[-0.103, -0.081]</t>
+          <t>-0.083***
+[-0.096, -0.071]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -634,8 +634,8 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.086***
-[-0.097, -0.075]</t>
+          <t>-0.077***
+[-0.090, -0.065]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>R² = .68, R²adj = .68, F(2, 35479) = 38497.98, p &lt; .0001, AIC = 66354.5, BIC = 66379.9, LL = -33174.2, MAE = 0.493, MAD = 0.471, N = 35481</t>
+          <t>R² = .66, R²adj = .66, F(2, 27562) = 26706.63, p &lt; .0001, AIC = 50967.9, BIC = 50992.6, LL = -25480.9, MAE = 0.490, MAD = 0.493, N = 27564</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>R² = .70, R²adj = .70, F(2, 35479) = 40952.81, p &lt; .0001, MAE = 0.492, MAD = 0.474, N = 35481</t>
+          <t>R² = .67, R²adj = .67, F(2, 27562) = 28292.68, p &lt; .0001, MAE = 0.489, MAD = 0.493, N = 27564</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">

--- a/results/tab02-2.xlsx
+++ b/results/tab02-2.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>H22(OLS)+full</t>
+          <t>H22(OLS)+nogeo</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -439,7 +439,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>H22(RLM)+full</t>
+          <t>H22(RLM)+nogeo</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
